--- a/verification/cases/roundtrip/shared_formulas/init.xlsx
+++ b/verification/cases/roundtrip/shared_formulas/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13BA8D76-676A-48C3-8F6A-B9C772628FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14940" windowHeight="8775"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Label" sheetId="5" r:id="rId1"/>
@@ -74,8 +80,21 @@
     <definedName name="PDOC\10_1\30_1___lab">#REF!</definedName>
     <definedName name="PDOC\10_1___lab">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <webPublishing codePage="65001"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -151,8 +170,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="arial"/>
@@ -200,13 +219,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -244,7 +271,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -278,6 +305,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -312,9 +340,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -487,21 +516,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:B41"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f t="shared" ref="A2:A41" si="0">B2</f>
         <v>ProductionOrderConfirmation</v>
@@ -510,7 +539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f t="shared" si="0"/>
         <v>RequiredAcceptanceDate</v>
@@ -519,7 +548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>Header</v>
@@ -528,7 +557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>UniqueDocumentNumberID</v>
@@ -537,7 +566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>ExpiryDateTime</v>
@@ -546,7 +575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>IssuingParty</v>
@@ -555,7 +584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>DEA</v>
@@ -564,7 +593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>ID</v>
@@ -573,7 +602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>FinalRecipientDEA</v>
@@ -582,7 +611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>ID</v>
@@ -591,7 +620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>RequirementPackaging</v>
@@ -600,7 +629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>LineItemNumberID</v>
@@ -609,7 +638,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>Description</v>
@@ -618,7 +647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>ID</v>
@@ -627,7 +656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>Code</v>
@@ -636,7 +665,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>Description</v>
@@ -645,7 +674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>ProductionOrderLineItem</v>
@@ -654,7 +683,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>LineItemNumberID</v>
@@ -663,7 +692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>Quantity</v>
@@ -672,7 +701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>quantityUnitCode</v>
@@ -681,7 +710,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>ProductItem</v>
@@ -690,7 +719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>Description</v>
@@ -699,7 +728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>Payment</v>
@@ -708,7 +737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>TotalAmount</v>
@@ -717,7 +746,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>OtherReference</v>
@@ -726,7 +755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>ID</v>
@@ -735,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>ReferenceType</v>
@@ -744,7 +773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>Code</v>
@@ -753,7 +782,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>OtherReference</v>
@@ -762,7 +791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>ID</v>
@@ -771,7 +800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>ReferenceType</v>
@@ -780,7 +809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>Code</v>
@@ -789,7 +818,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>OtherReference</v>
@@ -798,7 +827,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="0"/>
         <v>ID</v>
@@ -807,7 +836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="0"/>
         <v>ReferenceType</v>
@@ -816,7 +845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="0"/>
         <v>Code</v>
@@ -825,7 +854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
         <v>OtherReference</v>
@@ -834,7 +863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="0"/>
         <v>ID</v>
@@ -843,7 +872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="0"/>
         <v>ReferenceType</v>
@@ -852,7 +881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="0"/>
         <v>Code</v>
